--- a/output/STOCK_MATCH.xlsx
+++ b/output/STOCK_MATCH.xlsx
@@ -7,9 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DATA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="STOCK_RESULT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VARIANCE_REPORT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STOCK_RESULT'!$A$1:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VARIANCE_REPORT'!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,12 +53,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -413,57 +440,4242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I125"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Начальный остаток</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Приход</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Возврат поставщику</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Расчетный остаток</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Фактический остаток</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Расхождение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SKU-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Cherry 400 мл</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SKU-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Avocado 400 мл</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SKU-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Mango 400 мл</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SKU-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Blackberry 400 мл</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SKU-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Intense 400 мл</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SKU-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Charm 400 мл</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SKU-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Lovely Moments 400 мл</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SKU-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Argan Oil 400 мл</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SKU-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Keratin Extracts 400 мл</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SKU-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Lemon Oil 400 мл</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SKU-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Olive Oil 400 мл</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SKU-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Black 400 мл</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SKU-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Blue 400 мл</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SKU-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Almond 600 мл</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SKU-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Aloe Vera 600 мл</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SKU-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Garlic 600 мл</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SKU-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Keratin 600 мл</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SKU-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Mint 600 мл</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SKU-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Nettle 600 мл</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SKU-025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Baby 1 л</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SKU-026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SKU-027</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1 л</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SKU-028</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1 л</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SKU-029</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SKU-030</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dream 1 л</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SKU-031</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Black 1 л</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SKU-033</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Magina 1,44 л</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SKU-034</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1,44 л</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SKU-035</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lotos 1,44 л</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SKU-036</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Mango 1,44 л</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SKU-037</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dream 1,44 л</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SKU-038</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1,44 л</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SKU-040</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Papatya 1,44 л</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SKU-041</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1,44 л</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SKU-042</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Passion Fruit 1,44 л</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SKU-043</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Orchide 1,44 л</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SKU-044</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Saffran 1,44 л</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SKU-045</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Shaik 1,44 л</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SKU-046</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Jasmin 1,44 л</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SKU-047</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SKU-048</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1,44 л</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SKU-049</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Rose 1,44 л</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SKU-055</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Peony 2,7 л</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SKU-056</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Mountain Breeze 2,7 л</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SKU-058</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Vanilla 2,7 л</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SKU-059</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lavender 2,7 л</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SKU-060</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Rose 2,7 л</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SKU-063</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dahlia 2,7 л</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SKU-074</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant White 1 л</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SKU-075</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Dream 1 л</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SKU-076</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Floral Mist 1 л</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SKU-077</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Midnight 1 л</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SKU-078</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Spring 1 л</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SKU-079</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Sweet Tropic 1 л</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SKU-080</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Velvet 1 л</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SKU-081</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Black 1 л</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SKU-082</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 1 л</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SKU-083</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant White 1,5 л</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SKU-084</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Mango 1,5 л</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SKU-085</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Floral Mist 1,5 л</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SKU-086</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Midnight 1,5 л</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SKU-087</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Spring 1,5 л</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SKU-088</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Sweet Tropic 1,5 л</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SKU-089</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Velvet 1,5 л</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SKU-091</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Black 1,5 л</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SKU-093</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Baby 1,5 л</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SKU-110</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Lavanda 500 мл</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SKU-111</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Ocean 500 мл</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SKU-112</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Rose 500 мл</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SKU-113</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Olive 500 мл</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SKU-118</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Coconut 500 мл</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SKU-119</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oatmeal 500 мл</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SKU-120</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oriental 500 мл</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SKU-121</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Pine Forest 500 мл</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SKU-122</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Cherry 500 мл</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SKU-132</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Grapefruit 4×85 г</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SKU-133</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Bouquet 4×85 г</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SKU-134</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Green Tea 4×85 г</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SKU-135</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Sea Minerals 4×85 г</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SKU-136</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Bouquet 4×100 г</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SKU-137</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Sea Minerals 4×100 г</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SKU-138</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Rose 4×100 г</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SKU-139</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Pink 1 л</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SKU-141</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Purple 1 л</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SKU-142</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Purple 2,5 л</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SKU-143</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Отбеливатель SVO White 750 г</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SKU-144</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Отбеливатель SVO Color 750 г</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SKU-160</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SKU-161</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SKU-162</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SKU-163</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SKU-167</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SKU-169</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SKU-182</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SKU-183</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SKU-184</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SKU-185</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SKU-189</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SKU-191</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 2,7 кг</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SKU-204</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 4 кг</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SKU-205</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 4 кг</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SKU-206</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 4 кг</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SKU-207</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 4 кг</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SKU-211</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 4 кг</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SKU-213</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 4 кг</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SKU-215</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 6 кг</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SKU-216</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 6 кг</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SKU-217</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 6 кг</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SKU-218</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 6 кг</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SKU-224</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 6 кг</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SKU-226</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 9 кг</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SKU-227</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 9 кг</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SKU-228</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 9 кг</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SKU-229</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 9 кг</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SKU-235</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 9 кг</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SKU-256</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 750 мл</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SKU-257</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Grapefruit 750 мл</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SKU-258</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 750 мл</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SKU-259</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 750 мл</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SKU-279</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 4 л</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>748</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SKU-280</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Grapefruit 4 л</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SKU-281</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 4 л</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SKU-282</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 4 л</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SKU-291</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Baby 1,3 кг</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I125"/>
+  <conditionalFormatting sqref="I2:I125">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Начальный остаток</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Приход</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Возврат поставщику</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Расчетный остаток</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Фактический остаток</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Расхождение</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>